--- a/dataset_BEI_pemegang_saham_1persen.xlsx
+++ b/dataset_BEI_pemegang_saham_1persen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rifqii Kuliah\Semester 5\Data Mining\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB91BA4-6BDF-4884-93F7-B5D0015D4C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8004AB5B-51A5-4A45-98F9-970C7582F7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset 500 Baris" sheetId="1" r:id="rId1"/>
